--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N78_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N78_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.03750345437739</v>
+        <v>2.272516936002753</v>
       </c>
       <c r="D2" t="n">
-        <v>25.94790819947097</v>
+        <v>2.791775683222758</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4011805526706453</v>
+        <v>10.7802099906974</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3061504161257282</v>
+        <v>10.47071796287511</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,23 +512,87 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
+        <v>26.03750345437739</v>
+      </c>
+      <c r="D3" t="n">
+        <v>25.94790819947097</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10.7802099906974</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10.47071796287511</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>T2372</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W0066F0001T0006Z000C1N78.png</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
         <v>26.83986455971868</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>26.56020903172242</v>
       </c>
-      <c r="E3" t="n">
-        <v>0.4011805526706453</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.3061504161257282</v>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="E4" t="n">
+        <v>10.7802099906974</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10.47071796287511</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>T2372</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W0066F0001T0006Z000C1N78.png</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>8.370365730623073</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8.678266875943066</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10.7802099906974</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10.47071796287511</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>T2372</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N78_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0001T0006Z000C1N78_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>2.272516936002753</v>
+        <v>0.3692840021004473</v>
       </c>
       <c r="D2" t="n">
-        <v>2.791775683222758</v>
+        <v>0.4536635485236982</v>
       </c>
       <c r="E2" t="n">
-        <v>10.7802099906974</v>
+        <v>1.751784123488328</v>
       </c>
       <c r="F2" t="n">
-        <v>10.47071796287511</v>
+        <v>1.701491668967206</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.03750345437739</v>
+        <v>4.231094311336326</v>
       </c>
       <c r="D3" t="n">
-        <v>25.94790819947097</v>
+        <v>4.216535082414032</v>
       </c>
       <c r="E3" t="n">
-        <v>10.7802099906974</v>
+        <v>1.751784123488328</v>
       </c>
       <c r="F3" t="n">
-        <v>10.47071796287511</v>
+        <v>1.701491668967206</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.83986455971868</v>
+        <v>4.361477990954286</v>
       </c>
       <c r="D4" t="n">
-        <v>26.56020903172242</v>
+        <v>4.316033967654894</v>
       </c>
       <c r="E4" t="n">
-        <v>10.7802099906974</v>
+        <v>1.751784123488328</v>
       </c>
       <c r="F4" t="n">
-        <v>10.47071796287511</v>
+        <v>1.701491668967206</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.370365730623073</v>
+        <v>1.360184431226249</v>
       </c>
       <c r="D5" t="n">
-        <v>8.678266875943066</v>
+        <v>1.410218367340748</v>
       </c>
       <c r="E5" t="n">
-        <v>10.7802099906974</v>
+        <v>1.751784123488328</v>
       </c>
       <c r="F5" t="n">
-        <v>10.47071796287511</v>
+        <v>1.701491668967206</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
